--- a/data/trans_dic/IP31KM07_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM07_2023-Estudios-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>93,16%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>68,42; 96,79</t>
+          <t>86,47; 98,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>86,86; 98,15</t>
+          <t>82,01; 97,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>80,86; 96,24</t>
+          <t>87,71; 96,5</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>88,02%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>69,06; 91,54</t>
+          <t>81,56; 89,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>79,92; 88,53</t>
+          <t>87,31; 92,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>74,83; 88,64</t>
+          <t>85,36; 90,29</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,71%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>85,43; 93,96</t>
+          <t>86,64; 94,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>86,64; 93,86</t>
+          <t>85,35; 94,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>87,55; 92,91</t>
+          <t>87,73; 93,19</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>89,06%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>73,81; 91,2</t>
+          <t>84,85; 90,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>83,68; 89,68</t>
+          <t>88,01; 92,32</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>80,82; 89,25</t>
+          <t>87,0; 90,72</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>61</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>47476</t>
+          <t>50557</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>54975</t>
+          <t>42249</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>102451</t>
+          <t>92806</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>36740; 51974</t>
+          <t>46447; 52765</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>50677; 57265</t>
+          <t>37647; 44558</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>90597; 107830</t>
+          <t>87379; 96130</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>561</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>566</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>561</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>386187</t>
+          <t>400733</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>428428</t>
+          <t>383581</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>814615</t>
+          <t>784315</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>312024; 413599</t>
+          <t>380419; 417271</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>403820; 447319</t>
+          <t>370761; 393134</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>716228; 848392</t>
+          <t>760592; 804582</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>202</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>209</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>131750</t>
+          <t>152062</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>164568</t>
+          <t>132617</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>296317</t>
+          <t>284678</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>124884; 137363</t>
+          <t>144424; 157191</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>156939; 170012</t>
+          <t>125578; 138319</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>286563; 304125</t>
+          <t>275327; 292442</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>842</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>829</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>842</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>565414</t>
+          <t>603352</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>647971</t>
+          <t>558448</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1213384</t>
+          <t>1161799</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>481054; 594348</t>
+          <t>582763; 619772</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>623159; 667911</t>
+          <t>543623; 570247</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1128604; 1246377</t>
+          <t>1135000; 1183532</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP31KM07_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM07_2023-Estudios-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,290 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que toman legumbres más de una vez a la semana (tasa de respuesta: 100,0%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Primarios</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>94,12%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>92,04%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>93,16%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>86,47; 98,23</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>82,01; 97,06</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>87,71; 96,5</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>85,92%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>90,33%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>88,02%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>81,56; 89,46</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>87,31; 92,57</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>85,36; 90,29</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>91,23%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>90,13%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>90,71%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>86,64; 94,3</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>85,35; 94,01</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>87,73; 93,19</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>87,85%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>90,41%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>89,06%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>84,85; 90,24</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>88,01; 92,32</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>87,0; 90,72</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -828,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>133</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.9412073614473649</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.9203646190146316</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.9316030019999556</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>50557</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>42249</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>92806</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.8647001311872536</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.8201145445826959</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.8771276250977088</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>46447; 52765</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>37647; 44558</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>87379; 96130</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.9823077117036529</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.9706482182990503</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.9649699688575337</v>
       </c>
     </row>
     <row r="7">
@@ -901,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>561</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>566</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1127</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.8591621687616391</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.9032538310835904</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.880174920522147</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>400733</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>383581</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>784315</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.8156100816969835</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.8730657886093046</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.8535524933475063</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>380419; 417271</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>370761; 393134</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>760592; 804582</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.8946189440218753</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.9257483030027491</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.9029189650356424</v>
       </c>
     </row>
     <row r="10">
@@ -974,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>411</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.912264671037156</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.9012997244429176</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.9071236607029296</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>152062</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>132617</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>284678</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.8664428391668153</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.8534569770146404</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.8773252047601511</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>144424; 157191</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>125578; 138319</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>275327; 292442</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.9430359077351307</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.9400531986684727</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.9318629413600298</v>
       </c>
     </row>
     <row r="13">
@@ -1047,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>842</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>829</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1671</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.8784661877081333</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.9040599368905117</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.8905850984635028</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>603352</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>558448</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>1161799</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.8484900358767513</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.880059695629371</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.8700414781755567</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>582763; 619772</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>543623; 570247</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>1135000; 1183532</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.9023731598603605</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.9231611178856838</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.9072439665471055</v>
       </c>
     </row>
     <row r="16">
@@ -1129,4 +781,376 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que toman legumbres más de una vez a la semana (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>72</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>61</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>50557</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>42249</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>92806</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>46447</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>37647</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>87379</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>52765</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>44558</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>96130</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>561</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>566</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>400733</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>383581</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>784315</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>380419</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>370761</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>760592</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>417271</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>393134</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>804582</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>209</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>202</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>152062</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>132617</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>284678</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>144424</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>125578</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>275327</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>157191</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>138319</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>292442</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>842</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>829</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>1671</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>603352</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>558448</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>1161799</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>582763</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>543623</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>1135000</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>619772</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>570247</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>1183532</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>